--- a/合规平台条文整理（修改4.0）.xlsx
+++ b/合规平台条文整理（修改4.0）.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="349">
   <si>
     <t>中国-法律</t>
   </si>
@@ -7485,12 +7485,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF333333"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -7501,6 +7495,12 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -9334,7 +9334,9 @@
       <c r="Z12" s="45"/>
     </row>
     <row r="13" ht="400" customHeight="1" spans="1:26">
-      <c r="A13" s="5"/>
+      <c r="A13" s="5" t="s">
+        <v>35</v>
+      </c>
       <c r="B13" s="5" t="s">
         <v>91</v>
       </c>
@@ -9428,7 +9430,9 @@
       <c r="Z14" s="45"/>
     </row>
     <row r="15" ht="400" customHeight="1" spans="1:26">
-      <c r="A15" s="5"/>
+      <c r="A15" s="5" t="s">
+        <v>35</v>
+      </c>
       <c r="B15" s="5" t="s">
         <v>108</v>
       </c>
@@ -9674,7 +9678,9 @@
       <c r="Z20" s="44"/>
     </row>
     <row r="21" ht="56" spans="1:26">
-      <c r="A21" s="19"/>
+      <c r="A21" s="19" t="s">
+        <v>35</v>
+      </c>
       <c r="B21" s="29" t="s">
         <v>136</v>
       </c>
@@ -9940,7 +9946,9 @@
       <c r="Z26" s="44"/>
     </row>
     <row r="27" ht="98" spans="1:26">
-      <c r="A27" s="19"/>
+      <c r="A27" s="19" t="s">
+        <v>35</v>
+      </c>
       <c r="B27" s="19" t="s">
         <v>183</v>
       </c>
@@ -10100,7 +10108,9 @@
       <c r="Z29" s="58"/>
     </row>
     <row r="30" ht="84" spans="1:26">
-      <c r="A30" s="5"/>
+      <c r="A30" s="5" t="s">
+        <v>35</v>
+      </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5" t="s">
         <v>215</v>
@@ -10438,7 +10448,9 @@
       <c r="Z38" s="44"/>
     </row>
     <row r="39" ht="196" spans="1:26">
-      <c r="A39" s="5"/>
+      <c r="A39" s="5" t="s">
+        <v>35</v>
+      </c>
       <c r="B39" s="16" t="s">
         <v>253</v>
       </c>
@@ -11026,7 +11038,9 @@
       <c r="Z53" s="37"/>
     </row>
     <row r="54" ht="400" customHeight="1" spans="1:26">
-      <c r="A54" s="5"/>
+      <c r="A54" s="5" t="s">
+        <v>320</v>
+      </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5" t="s">
         <v>334</v>
@@ -11104,7 +11118,9 @@
       <c r="Z55" s="37"/>
     </row>
     <row r="56" ht="400" customHeight="1" spans="1:26">
-      <c r="A56" s="2"/>
+      <c r="A56" s="2" t="s">
+        <v>320</v>
+      </c>
       <c r="B56" s="2"/>
       <c r="C56" s="2" t="s">
         <v>341</v>
@@ -11134,7 +11150,9 @@
       <c r="Z56" s="2"/>
     </row>
     <row r="57" ht="400" customHeight="1" spans="1:26">
-      <c r="A57" s="2"/>
+      <c r="A57" s="2" t="s">
+        <v>320</v>
+      </c>
       <c r="B57" s="2" t="s">
         <v>342</v>
       </c>
@@ -11172,7 +11190,9 @@
       </c>
     </row>
     <row r="58" ht="400" customHeight="1" spans="1:26">
-      <c r="A58" s="2"/>
+      <c r="A58" s="2" t="s">
+        <v>320</v>
+      </c>
       <c r="B58" s="2"/>
       <c r="C58" s="4" t="s">
         <v>345</v>
@@ -11209,7 +11229,9 @@
     </row>
     <row r="59" spans="1:26">
       <c r="A59" s="2"/>
-      <c r="B59" s="2"/>
+      <c r="B59" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="C59" s="4" t="s">
         <v>341</v>
       </c>
@@ -11239,9 +11261,7 @@
     </row>
     <row r="60" spans="1:26">
       <c r="A60" s="2"/>
-      <c r="B60" s="2" t="s">
-        <v>348</v>
-      </c>
+      <c r="B60" s="2"/>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
